--- a/results/climate_change_breakdown/2050/propanol production, DAC carbon dioxide, wind hydrogen, fossil ethylene_GLO.xlsx
+++ b/results/climate_change_breakdown/2050/propanol production, DAC carbon dioxide, wind hydrogen, fossil ethylene_GLO.xlsx
@@ -441,7 +441,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>1.132158286271689</v>
+        <v>0.9912521579352603</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -475,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.1297226037580513</v>
+        <v>0.1297226037580512</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -492,7 +492,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.9114027988054948</v>
+        <v>0.9114027988054954</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.1736926972099948</v>
+        <v>0.03337082123802784</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.0002984168386191952</v>
+        <v>1.275457513260016E-05</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.0004027091605940047</v>
+        <v>0.0001041170800061068</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -560,7 +560,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>0.0006344627436349341</v>
+        <v>0.000634462743634921</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -577,7 +577,7 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>3.535064954862282E-05</v>
+        <v>3.535064954862075E-05</v>
       </c>
       <c r="E10">
         <v>1</v>
